--- a/site/HR-ITSM-Freshservice-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-Freshservice-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1186,6 +1186,50 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01M5XZPYSSDDYZWCHJTKMVXFEH</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Integration-Guide/#h_01M5XZPYSSDDYZWCHJTKMVXFEH</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Supported Attributes for Change event</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01M5Y0JZXTCYW8S1F8QK9JAJTV</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Freshservice-Integration-Guide/#h_01M5Y0JZXTCYW8S1F8QK9JAJTV</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
